--- a/OUT_EXCEL/out_10.xlsx
+++ b/OUT_EXCEL/out_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,27 +457,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LOP</t>
+          <t>LớP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HO TEN</t>
+          <t>HO TÊN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MA SINH VIEN</t>
+          <t>MÃ SINH VIÊN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CHUC VU</t>
+          <t>CHỨC VU</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>sO dien thoAl</t>
+          <t>SÓ ĐlÉN THOAI</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>GHI CHU</t>
+          <t>GHI CHÚ</t>
         </is>
       </c>
     </row>
@@ -498,17 +498,17 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DUONG QUANG DU</t>
+          <t>DƯƠNG QUANG Dự</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B20DCCN157</t>
+          <t>BZODCCN157</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lop truong</t>
+          <t>Lớp trưởng</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>duongdu202@gmail.com</t>
+          <t>duongdu202@gmail com</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -530,17 +530,17 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NGUYEN TH! KIM NGAN</t>
+          <t>NGUYEN THỊ KIM NGẪN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B20DCCN469</t>
+          <t>BZODCCN469</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bi thur</t>
+          <t>Bí thư</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>nganhhbg1234@gmail.com</t>
+          <t>nganhhbg 1234@gmail com</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -561,22 +561,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D20CNPM1</t>
+          <t>D2OCNPM1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NGUYEN PHUONG NAM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>B20DCCN457</t>
-        </is>
-      </c>
+          <t>NGUYÊN PHUONG NAM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lop pho</t>
+          <t>Lớp phó</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -586,7 +582,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>namnp.201002@gmail.com</t>
+          <t>namnp 201002@gmail com</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -598,17 +594,17 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NGUYEN DINH MANH QUYNH</t>
+          <t>NGUYỄN ĐINH MANH QUỸNH</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B20DCCN567</t>
+          <t>BZODCCN567</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lop trurong</t>
+          <t>Lớp trưởng</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -618,7 +614,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>nguyendinhmanhquynh@gmail.com</t>
+          <t>nguyendinhmanhquynh@gmail com</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -630,17 +626,17 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NGUYEN VAN LINH</t>
+          <t>NGUYẾN VĂN LINH</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B20DCCN400</t>
+          <t>BZODCCN4OO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lop pho</t>
+          <t>Lớp phó</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -655,24 +651,16 @@
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>D20CNPM2</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NGUYEN VAN TUAN ANH</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>B20DCCN064</t>
-        </is>
-      </c>
+          <t>NGUYỀN VĂN TUAN ANH</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lop pho</t>
+          <t>Lớp phó</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -688,19 +676,15 @@
         <v>7</v>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>NGUYEN HOU TUAN</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B20DCCN616</t>
+          <t>BZODCCN616</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lop truong</t>
+          <t>Lớp truong</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -710,7 +694,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tuannh.b20cn616@stu.ptit.edu.vn</t>
+          <t>Iuannh b20cn6 16@stu ptit eduvn</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -722,17 +706,17 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DO NGOC NHI</t>
+          <t>ĐỖ NGỌC NHI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B20DCCN486</t>
+          <t>BZODCCN486</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Lop pho</t>
+          <t>Lớp phó</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -742,7 +726,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>dongocnhi0110@gmail.com</t>
+          <t>dongocnhio 110 @gmail com</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -753,7 +737,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D20CNPM3</t>
+          <t>D2OCNPM3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -763,12 +747,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B20DCCN317</t>
+          <t>BZODCCN317</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lop pho</t>
+          <t>Lớp phó</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -778,7 +762,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>nguyenqhuy02@gmail.com</t>
+          <t>nguyenghuy02@gmail com</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -790,17 +774,13 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BUI HONG SON</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>B20DCCN572</t>
-        </is>
-      </c>
+          <t>BÙl HỒNG SƠN</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lop truong</t>
+          <t>Lớp trường</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -810,7 +790,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>hongson1234abb@gmail.com</t>
+          <t>hongson 7234abb@gmail com</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -822,27 +802,23 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PHAM TUNG DUONG</t>
+          <t>PHAM TÙNG DUƠNG</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B20DCCN163</t>
+          <t>BZODCCN163</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lop pho</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0969613858</t>
-        </is>
-      </c>
+          <t>Lớp phó</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>phamtungduong06032002@gmail.com</t>
+          <t>phamtungduongo6032002@gmail com</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -851,16 +827,28 @@
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>D20CNPM4</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Vũ Trọng Hỉễu</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Lớp trưởng</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0971710602</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>vuhieu dev@gmail com</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -870,29 +858,21 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vu Trong Hieu</t>
+          <t>Nguyễn Tiễn Hùng</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B20DCCN262</t>
+          <t>BZODCCN</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lop truong</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0971110602</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>vuhieu.dev@gmail.com</t>
-        </is>
-      </c>
+          <t>Lớp phó</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -902,55 +882,51 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nguyen Tien Hung</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>B20DCCN</t>
-        </is>
-      </c>
+          <t>Phạm Thị Phương Anh</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lop pho</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+          <t>Zớp phó</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0393706083</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>anhhuyenhuy1912@gmail com</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>D20CNPM5</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pham Thi Phuong Anh</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>B20DCCN071</t>
-        </is>
-      </c>
+          <t>Vũ Nguyệt Hà</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lop pho</t>
+          <t>Lớp trờng; Bí thư</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0393706083</t>
+          <t>0975715292</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>anhhuyenhuy1912@gmail.com</t>
+          <t>ha anho2nb@gmail com</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -962,27 +938,27 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Vu Nguyet Ha</t>
+          <t>Phan Tuẫn Thạch</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B20DCCN216</t>
+          <t>BZODCCN635</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lop truong. Bi thu</t>
+          <t>Lớp phó</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0975715292</t>
+          <t>0854352262</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ha.anh02nb@gmail.com</t>
+          <t>Phantuanthachuu@gmail com</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -991,48 +967,48 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Phan Tuan Thach</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>B20DCCN635</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Lop pho</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0854352262</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Phantuanthachuu@gmail.com</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D2OCNPMG</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>D20CNPM6</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Nguyen Đinh Trung</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BZODCCN698</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Lớp trường</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0389403869</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>nguyendinhtrung16072002@gmail com</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1042,27 +1018,27 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nguyen Dinh Trung</t>
+          <t>Nguyễn Minh Hiễu</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B20DCCN698</t>
+          <t>BZODCCN253</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lop truong</t>
+          <t>7ớp phó</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0389403869</t>
+          <t>0967683318</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>nguyendinhtrung16072002@gmail.com</t>
+          <t>minhhieulspt@gmail com</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1071,30 +1047,34 @@
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>D2OHTTT1</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nguyen Minh Hieu</t>
+          <t>Vũ Quang Hân</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>B20DCCN253</t>
+          <t>BZODCCNO17</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Iop pho</t>
+          <t>Ìớp phó</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0967683318</t>
+          <t>0353391536</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>minhhieulspt@gmail.com</t>
+          <t>quanghano610@gmail com</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1103,34 +1083,30 @@
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>D20httt1</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vu Quang Han</t>
+          <t>Phan Anh Tuẫn</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B20DCCN017</t>
+          <t>BZODCCNO4O</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Iop pho</t>
+          <t>Lớp trưòng; Bí Thu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0353391536</t>
+          <t>0829196098</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>quanghan0610@gmail.com</t>
+          <t>TuanPA BZOCNO4O @stu ptit edu.vn</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -1142,27 +1118,27 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phan Anh Tuan</t>
+          <t>Nguyễn Tiễn Hưng</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>B20DCCN040</t>
+          <t>BZODCCN347</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lop truong, Bi Thur</t>
+          <t>Lớp phó</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0829196098</t>
+          <t>0374748599</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>TuanPA.B20CN040@stu.ptit.edu.vn</t>
+          <t>HungNT.BZOCN341@stu ptit edu.vn</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1171,30 +1147,34 @@
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D2OHTTT2</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nguyen Tien Hung</t>
+          <t>Nguyễn Lê Trúc Quỳnh</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>B20DCCN341</t>
+          <t>BZODCCN568</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Lop pho</t>
+          <t>Zớp phó</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0374748599</t>
+          <t>0329484673</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>HungNT.B20CN341@stu.ptit.edu.vn</t>
+          <t>QuynhNLT.B2OCN568@stu ptit edu.vn</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1203,34 +1183,30 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>D20HTTT2</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nguyen Le Truc Quynh</t>
+          <t>Vương Thị Uyên</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B20DCCN568</t>
+          <t>BZODCCN716</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lop pho</t>
+          <t>Léptuong</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0329484673</t>
+          <t>0898587866</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>QuynhNLT.B20CN568@stu.ptit.edu.vn</t>
+          <t>uyenvuong411@gmail com</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1242,27 +1218,27 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Vuong Thj Uyen</t>
+          <t>Tnan Minh @uang</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B20DCCN716</t>
+          <t>BZODCCN538</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lop truong</t>
+          <t>Lớp phó</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0898587866</t>
+          <t>0933465567</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>uyenvuong411@gmail.com</t>
+          <t>tm921012002@gmail. com</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1271,30 +1247,34 @@
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>D2OHTTT3</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tran Minh Quang</t>
+          <t>Tỗng Tiễn Đat</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B20DCCN538</t>
+          <t>BZODCCN178</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lop pho</t>
+          <t>Lớp phó</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0933465567</t>
+          <t>0984035467</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>tmq21012002@gmail.com</t>
+          <t>datti260602@gmail com</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1303,34 +1283,30 @@
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>D20HTTT3</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tong Tien Dat</t>
+          <t>Nguyễn Thu Nga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B20DCCN178</t>
+          <t>BZODCCN468</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lop pho</t>
+          <t>Lớp trường</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0984035467</t>
+          <t>70967560815</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>dattt260602@gmail.com</t>
+          <t>nguyenngabin @gmail com</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1342,86 +1318,54 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nguyen Thu Nga</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>B20DCCN468</t>
-        </is>
-      </c>
+          <t>Nguyễn Đông Hoàng</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lop truong</t>
+          <t>Zớp phó</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0967560815</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>nguyenngabin@gmail.com</t>
-        </is>
-      </c>
+          <t>0867170702</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D2OHTTT4</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nguyen Dong Hoang</t>
+          <t>Dương Thị Thanh Tâm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>B20DCCN276</t>
+          <t>BZODCCN588</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lop pho</t>
+          <t>Zớp phó</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0867170702</t>
+          <t>0931508545</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>D20HTTT4</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Durong Thi Thanh Tam</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Lop pho</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>0931508545</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
